--- a/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -2702,17 +2694,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -2793,17 +2777,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -2884,17 +2860,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -2975,17 +2943,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -3066,17 +3026,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -3157,17 +3109,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -3248,17 +3192,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -3338,16 +3274,8 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3391,16 +3319,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3444,16 +3364,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3497,16 +3409,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3550,16 +3454,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3603,16 +3499,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3656,16 +3544,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3709,16 +3589,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3762,16 +3634,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3815,16 +3679,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3868,16 +3724,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3921,16 +3769,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3974,16 +3814,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4027,16 +3859,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4080,16 +3904,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4133,16 +3949,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2244A02</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>7782007</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4186,16 +3994,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4239,16 +4039,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4292,16 +4084,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4345,16 +4129,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4398,16 +4174,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4451,16 +4219,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4504,16 +4264,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4557,16 +4309,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4610,16 +4354,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4663,16 +4399,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4716,16 +4444,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4769,16 +4489,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2244008</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4822,16 +4534,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4875,16 +4579,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4928,16 +4624,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4981,16 +4669,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5034,16 +4714,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5087,16 +4759,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5140,16 +4804,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5193,16 +4849,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5246,16 +4894,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5299,16 +4939,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5352,16 +4984,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5405,16 +5029,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>7781009</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5458,16 +5074,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5511,16 +5119,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5564,16 +5164,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5617,16 +5209,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5670,16 +5254,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5723,16 +5299,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5776,16 +5344,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5829,16 +5389,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5882,16 +5434,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5935,16 +5479,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5988,16 +5524,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6041,16 +5569,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW66"/>
+  <dimension ref="A1:AW81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2895,11 +2895,11 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3288,29 +3288,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>999</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>10</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3468,21 +3468,21 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>110</v>
+        <v>999</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3513,29 +3513,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>110</v>
+        <v>999</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>15</v>
+        <v>999</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>110</v>
+        <v>999</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3648,12 +3648,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3752,15 +3752,15 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3838,11 +3838,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3883,11 +3883,11 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3928,11 +3928,11 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -3963,29 +3963,29 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>100</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>999</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4008,12 +4008,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>110</v>
+        <v>999</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>110</v>
+        <v>999</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4143,21 +4143,21 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>110</v>
+        <v>999</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4188,29 +4188,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>10</v>
+        <v>999</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4233,21 +4233,21 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4278,12 +4278,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4413,29 +4413,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>A999</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>110</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>999</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>15</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4503,21 +4503,21 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4638,12 +4638,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4652,15 +4652,15 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4738,11 +4738,11 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4783,11 +4783,11 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4863,29 +4863,29 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4953,21 +4953,21 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4998,21 +4998,21 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -5043,21 +5043,21 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5106,11 +5106,11 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>10</v>
+        <v>999</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5223,12 +5223,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5331,11 +5331,11 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>15</v>
+        <v>999</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5556,11 +5556,11 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5608,6 +5608,681 @@
         <v>0</v>
       </c>
       <c r="O66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>110</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>10</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>110</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>15</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>110</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>20</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>110</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>999</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X110</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>110</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>100</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>10</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>100</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>15</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>100</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>20</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>100</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>999</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>100</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>999</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>10</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>999</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>15</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>999</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>20</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>999</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>999</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>999</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4264,8 +4930,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4309,8 +4998,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4354,8 +5066,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4399,8 +5134,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4444,8 +5202,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4489,8 +5270,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4534,8 +5338,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4579,8 +5406,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4624,8 +5474,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4669,8 +5542,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4714,8 +5610,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4759,8 +5678,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4804,8 +5746,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4849,8 +5814,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4894,8 +5882,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4939,8 +5950,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4984,8 +6018,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5029,8 +6086,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5074,8 +6154,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5119,8 +6222,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5164,8 +6290,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5209,8 +6358,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5254,8 +6426,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5299,8 +6494,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5344,8 +6562,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5389,8 +6630,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5434,8 +6698,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5479,8 +6766,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5524,8 +6834,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5569,8 +6902,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5614,8 +6970,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5659,8 +7038,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5704,8 +7106,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5749,8 +7174,31 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5794,8 +7242,31 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5839,8 +7310,31 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5884,8 +7378,31 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5929,8 +7446,31 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5974,8 +7514,31 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6019,8 +7582,31 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6064,8 +7650,31 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6109,8 +7718,31 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6154,8 +7786,31 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6199,8 +7854,31 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6244,8 +7922,31 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW81"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2971,15 +2971,15 @@
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>999</v>
+        <v>10</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3369,12 +3369,12 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3485,15 +3485,15 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3675,21 +3675,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3743,21 +3743,21 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3811,29 +3811,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3879,21 +3879,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X110</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4169,11 +4169,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>999</v>
+        <v>10</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4287,12 +4287,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4509,11 +4509,11 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4627,21 +4627,21 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4695,21 +4695,21 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>999</v>
+        <v>110</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4763,21 +4763,21 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4831,29 +4831,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>999</v>
+        <v>15</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4899,21 +4899,21 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -4921,3069 +4921,9 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>110</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>10</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>110</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>15</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>110</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>20</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>110</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>999</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>110</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>100</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>10</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>100</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>15</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>100</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>20</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>100</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>999</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>100</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>999</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>10</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>999</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>15</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>999</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>20</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>999</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>999</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>999</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>110</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>10</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>110</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>15</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>110</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>20</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>110</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>999</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>110</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>100</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>10</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>100</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>15</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>100</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N59" t="n">
-        <v>20</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>100</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N60" t="n">
-        <v>999</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>100</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>999</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>10</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>999</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>15</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>999</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>20</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>999</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>999</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>999</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>110</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>10</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>110</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>15</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>110</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>20</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>110</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>999</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>110</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>100</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>10</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>100</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>15</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>100</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>20</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>100</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>999</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>100</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>999</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>10</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>999</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>15</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>999</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>20</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>999</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>999</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2244001</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>999</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
@@ -3231,22 +3231,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -3334,22 +3334,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3436,22 +3436,22 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3504,22 +3504,22 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3572,22 +3572,22 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3640,22 +3640,22 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3708,22 +3708,22 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3776,22 +3776,22 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3844,22 +3844,22 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3912,22 +3912,22 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3980,22 +3980,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4048,22 +4048,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4116,22 +4116,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4252,22 +4252,22 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4320,22 +4320,22 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4388,22 +4388,22 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4456,22 +4456,22 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4524,22 +4524,22 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4592,22 +4592,22 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4660,22 +4660,22 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4728,22 +4728,22 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4796,22 +4796,22 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4864,22 +4864,22 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">

--- a/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00027_2244_케어백간병플러스보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
+  <dimension ref="A1:AW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2922,22 +2922,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -3025,22 +3025,22 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -3128,22 +3128,22 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2244A01</t>
+          <t>2244A02</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>2244001</t>
+          <t>2244002</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -3231,22 +3231,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2244A02</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2244002</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -3334,22 +3334,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2244A02</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2244002</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3436,22 +3436,22 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>2244A02</t>
+          <t>2244A03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2244002</t>
+          <t>2244003</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3504,22 +3504,22 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>2244A02</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2244002</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3572,22 +3572,22 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>2244A02</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2244002</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3640,22 +3640,22 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>2244A02</t>
+          <t>2244A04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2244002</t>
+          <t>2244004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(2년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X110</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3708,22 +3708,22 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>2244A03</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2244003</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3776,22 +3776,22 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>2244A03</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2244003</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3844,22 +3844,22 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>2244A03</t>
+          <t>2244A05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2244003</t>
+          <t>2244005</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3904,1026 +3904,6 @@
         <v>20</v>
       </c>
       <c r="O21" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2244003</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>100</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>10</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2244003</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>100</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>15</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2244A03</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2244003</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(5년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>100</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>20</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2244004</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>110</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>10</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2244004</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>110</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>15</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2244004</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>110</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>20</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2244004</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>100</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>10</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2244004</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>100</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>15</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2244A04</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2244004</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(10년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>100</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>20</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>110</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>10</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>110</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>15</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>X110</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>110</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>20</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>100</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>10</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>100</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>15</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2244A05</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2244005</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 케어백간병플러스보험 무배당 일반가입형 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>100</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>20</v>
-      </c>
-      <c r="O36" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
